--- a/data/trans_orig/IP16_n_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11045</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>22819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>47231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23407</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>27378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47223</t>
+          <t>47375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>30445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24554</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35662</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62821</t>
+          <t>62799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13148</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24138</t>
+          <t>24718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17732</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33225</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25136</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>37946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31787</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56965</t>
+          <t>57125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>48140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65808</t>
+          <t>66271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93218</t>
+          <t>92190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119813</t>
+          <t>118258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78111</t>
+          <t>77648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96121</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>149411</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176006</t>
+          <t>177034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32572</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26647</t>
+          <t>27194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55149</t>
+          <t>55281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66385</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25280</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38931</t>
+          <t>39406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48733</t>
+          <t>49255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53524</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62693</t>
+          <t>62431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96249</t>
+          <t>96466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109790</t>
+          <t>109731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22944</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>28698</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47592</t>
+          <t>46756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55160</t>
+          <t>55018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16038</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23498</t>
+          <t>23664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>22972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35312</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45423</t>
+          <t>45618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,67%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>18904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>37709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>60077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>143251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>246197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269301</t>
+          <t>268565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35749</t>
+          <t>35569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>44417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10380</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,47 +5020,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>10121</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>6195</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>15765</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>18,47%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>10121</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>6269</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>15895</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>39125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41360</t>
+          <t>41747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,47 +5133,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>81,57%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>75214</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>69570</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>79140</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>88,14%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>81,53%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>75214</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>69440</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>79066</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>88,14%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>81,37%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27965</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34477</t>
+          <t>34421</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>25112</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56093</t>
+          <t>56507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65136</t>
+          <t>65269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21491</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42827</t>
+          <t>42906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>117068</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111589</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207705</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12022</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>21037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26763</t>
+          <t>27048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26272</t>
+          <t>25796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>42168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38093</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22221</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53034</t>
+          <t>53439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69335</t>
+          <t>69811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>73,02%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>22965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>28201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45387</t>
+          <t>44407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60820</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>13981</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>28546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45008</t>
+          <t>45067</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>57064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73997</t>
+          <t>74355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36648</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51169</t>
+          <t>50711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97641</t>
+          <t>97582</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125935</t>
+          <t>124651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,38%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>64467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49952</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73332</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>130359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>147965</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>109441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16_n_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R2-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8534</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4907</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12865</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7688</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4365</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11655</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4141</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11606</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>26,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8534</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4635</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13095</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21121</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16790</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24748</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21347</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17380</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24670</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17429</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24894</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>73,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21121</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16560</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25020</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>36882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47231</t>
+          <t>47455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20969</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15120</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26616</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>17731</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12776</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23083</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12956</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22825</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>41,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>53,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20969</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15752</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27378</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,15%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31382</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47375</t>
+          <t>46233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29991</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24344</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35840</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>25490</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20138</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30445</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>20396</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30265</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>58,98%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>29991</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23582</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35208</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>58,85%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>47948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62799</t>
+          <t>62666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10013</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6414</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13800</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8747</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5373</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12720</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12412</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10013</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6300</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14237</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13853</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10066</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17452</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>13760</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9787</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17134</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10095</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17401</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>61,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13853</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>9629</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>17566</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>58,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32927</t>
+          <t>32489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17747</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13091</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22686</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>57,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13771</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9590</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18943</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9926</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18736</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>45,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>62,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17747</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12470</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22535</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25447</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37946</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21691</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16752</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>26347</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>55,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>42,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16772</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11600</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20953</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11807</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20617</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>54,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>37,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>21691</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>16903</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>26968</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>55,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>44622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>57263</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>48060</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66398</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>47937</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>39714</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>57125</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>39115</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>57055</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,26%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>57263</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>48140</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>66271</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92190</t>
+          <t>92603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>119116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>86656</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>77521</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>95859</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>53,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>77368</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>68180</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>85591</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>68250</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>86190</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>61,74%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>86656</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>77648</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>95779</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>60,21%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150966</t>
+          <t>150108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177034</t>
+          <t>176621</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2012 (tasa de respuesta: 99,54%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6397</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3086</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11067</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7163</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4001</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12136</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3917</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11733</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6397</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11232</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,65%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>19922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>32029</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27359</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35340</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29334</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24361</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32496</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24764</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>32580</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>32029</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27194</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>35613</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55281</t>
+          <t>55001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66404</t>
+          <t>66366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>8597</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13900</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>9293</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4910</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14759</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5133</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14728</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8597</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4934</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14119</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25063</t>
+          <t>25170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58768</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53465</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>62471</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>44872</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39406</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49255</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>39437</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>49032</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>58768</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>53246</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>62431</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,24%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96466</t>
+          <t>96359</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>109544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67365</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2438</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3263</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1172</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6798</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6970</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2438</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6197</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25477</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21801</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27254</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>26607</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23072</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28698</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22900</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>28717</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25477</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>21718</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27271</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>46695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55018</t>
+          <t>55207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8265</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6751</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3505</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11495</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11126</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,85%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4412</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7831</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20456</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16603</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23015</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>66,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20418</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15674</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23664</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16043</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24049</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>75,15%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>20456</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>17037</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>22972</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35383</t>
+          <t>35746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45618</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21844</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15257</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30041</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>26470</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18904</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35340</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19392</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34820</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,92%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>21844</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>15323</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30154</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37709</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>60635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>136730</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>128533</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143317</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,22%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>121231</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>112361</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128797</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>112881</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128309</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>82,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>136730</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>128420</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143251</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,22%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246197</t>
+          <t>245639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268565</t>
+          <t>268062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>158574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>158574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5941</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3198</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9763</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4375</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7991</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8131</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,18%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5941</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3043</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18035</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14213</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20778</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22658</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19042</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25202</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18902</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25003</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,82%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18035</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13817</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20933</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>75,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35569</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44417</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3968</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7641</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6153</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3114</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10672</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2951</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7941</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39128</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35455</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41323</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>36086</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31567</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39125</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32030</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39288</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>85,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>74,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39128</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>35155</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41747</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>69706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79140</t>
+          <t>79534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3737</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7978</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4166</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8634</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8140</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8334</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29709</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25468</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32059</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31958</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27490</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34421</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27984</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34404</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>29709</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>25112</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32070</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,83%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56507</t>
+          <t>55503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>65420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7077</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4192</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4297</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7345</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19406</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15681</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21477</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>20769</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17873</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17768</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,13%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>80,52%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>19406</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>15413</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>21446</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>55</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35947</t>
+          <t>35974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42906</t>
+          <t>42857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,74 +5989,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16998</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11520</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23909</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>15989</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10393</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22664</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10223</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>22667</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>12,54%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>17,78%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>16998</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11485</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>24391</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42264</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>106278</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>99367</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>111756</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>111472</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>104797</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117068</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>104794</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>117238</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>87,46%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>82,22%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>106278</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>98885</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>111791</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208473</t>
+          <t>207826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225537</t>
+          <t>225888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si consumen más de dos medicamentos en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si han consumido más de dos medicamentos en las últimas 2 semanas en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6171</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8838</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8296</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5532</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11272</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51,9%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11578</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21037</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11262</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8595</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13778</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>49,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7687</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4711</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10451</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>48,1%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26762</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18123</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13279</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23232</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>43,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>32,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>56,34%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13022</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8168</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18460</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27048</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33639</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25796</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42168</t>
+          <t>37140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23112</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18003</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27956</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>56,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>43,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>67,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>33601</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28163</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>38455</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,07%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28367</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>24142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>33345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>61968</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53439</t>
+          <t>44991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69811</t>
+          <t>58620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11575</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17302</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>39,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18192</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13380</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22965</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>48,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23645</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>38059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32396</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26669</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>18959</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14186</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23771</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>51,03%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>63,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28201</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53282</t>
+          <t>51903</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44407</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>59639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13555</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27719</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11153</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3602</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20893</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45067</t>
+          <t>41579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42227</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34594</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48758</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>66804</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>57064</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>74355</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43753</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>32789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50711</t>
+          <t>43030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>110557</t>
+          <t>80627</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97582</t>
+          <t>70714</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124651</t>
+          <t>88760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55955</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46133</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66628</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,97%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,39%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>50663</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30581</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>64467</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61204</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>40244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72760</t>
+          <t>58311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>105583</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85984</t>
+          <t>93209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130359</t>
+          <t>120878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>108997</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>98324</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>118819</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,61%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>72,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>127052</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>113248</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>147134</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,49%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,79%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>120997</t>
+          <t>93364</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109441</t>
+          <t>84681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132174</t>
+          <t>102748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>248048</t>
+          <t>202361</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229557</t>
+          <t>187066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273932</t>
+          <t>214735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>69,73%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
